--- a/documentation/excelFormat/warehouse_items(AutoRecovered).xlsx
+++ b/documentation/excelFormat/warehouse_items(AutoRecovered).xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\Hybrid_warehouse_V2.0\TheWarehouseAppV2.0\www\documentation\excelFormat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\Hybrid_warehouse_V2.0\www\documentation\excelFormat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D05374-5E29-4EF4-9966-A96DFE985D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EEE9C0-99B6-46E3-B60A-9C116D0687BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{F0D138BC-C464-4679-821F-721C5A793675}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1330,1266 +1330,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F98E668-5667-4278-8F3E-55E86133D308}">
-  <dimension ref="A1:L110"/>
-  <sheetFormatPr defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.08984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="C2">
-        <v>1450</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1908</v>
-      </c>
-      <c r="E2">
-        <v>2109</v>
-      </c>
-      <c r="F2" s="2">
-        <v>12</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="H2" s="6">
-        <v>46277</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="L2" s="6">
-        <v>46002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="C3">
-        <v>2100</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2450</v>
-      </c>
-      <c r="E3">
-        <v>2890</v>
-      </c>
-      <c r="F3" s="2">
-        <v>34</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="H3" s="6">
-        <v>46278</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="L3" s="6">
-        <v>46003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="C4">
-        <v>1400</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1679</v>
-      </c>
-      <c r="E4">
-        <v>1980</v>
-      </c>
-      <c r="F4" s="2">
-        <v>20</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="H4" s="6">
-        <v>46279</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="L4" s="6">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="C5">
-        <v>2140</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2430</v>
-      </c>
-      <c r="E5">
-        <v>2560</v>
-      </c>
-      <c r="F5" s="2">
-        <v>15</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="H5" s="6">
-        <v>46280</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="L5" s="6">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="C6">
-        <v>120</v>
-      </c>
-      <c r="D6" s="2">
-        <v>230</v>
-      </c>
-      <c r="E6">
-        <v>340</v>
-      </c>
-      <c r="F6" s="2">
-        <v>9</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="H6" s="6">
-        <v>46281</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="L6" s="6">
-        <v>46077</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="D7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="6"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="D8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="6"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="D9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="6"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="D10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="6"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="D11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="6"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="D12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="6"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="D13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="6"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="D14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="6"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="D15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="6"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="D16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="6"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="D17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="6"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="D18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="6"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="D19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="6"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="D20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="6"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="6"/>
-    </row>
-    <row r="21" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="D21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="6"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="6"/>
-    </row>
-    <row r="22" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="D22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="6"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="D23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="6"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="D24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="6"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="6"/>
-    </row>
-    <row r="25" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="D25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="6"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="6"/>
-    </row>
-    <row r="26" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="D26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="6"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="6"/>
-    </row>
-    <row r="27" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="D27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="6"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="6"/>
-    </row>
-    <row r="28" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="D28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="6"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="D29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="6"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="6"/>
-    </row>
-    <row r="30" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="D30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="6"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="D31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="6"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="D32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="6"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="D33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="6"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="D34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="6"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="D35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="6"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="D36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="6"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="6"/>
-    </row>
-    <row r="37" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="D37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="6"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="D38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="6"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="D39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="6"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="D40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="6"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="6"/>
-    </row>
-    <row r="41" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="D41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="6"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="6"/>
-    </row>
-    <row r="42" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="D42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="6"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="6"/>
-    </row>
-    <row r="43" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="D43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="6"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="6"/>
-    </row>
-    <row r="44" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="D44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="6"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="6"/>
-    </row>
-    <row r="45" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="D45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="6"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="6"/>
-    </row>
-    <row r="46" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="D46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="6"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="6"/>
-    </row>
-    <row r="47" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="D47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="6"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="6"/>
-    </row>
-    <row r="48" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="D48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="6"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="6"/>
-    </row>
-    <row r="49" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="D49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="6"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="6"/>
-    </row>
-    <row r="50" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="D50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="6"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="6"/>
-    </row>
-    <row r="51" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="D51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="6"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="D52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="6"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="D53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="6"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="6"/>
-    </row>
-    <row r="54" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="D54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="6"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="6"/>
-    </row>
-    <row r="55" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="D55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="6"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="6"/>
-    </row>
-    <row r="56" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="D56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="6"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="6"/>
-    </row>
-    <row r="57" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="D57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="6"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="6"/>
-    </row>
-    <row r="58" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="D58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="6"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="6"/>
-    </row>
-    <row r="59" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="D59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="6"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="6"/>
-    </row>
-    <row r="60" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="D60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="6"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="6"/>
-    </row>
-    <row r="61" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="D61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="6"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="6"/>
-    </row>
-    <row r="62" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="D62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="6"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="D63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="6"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="D64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="6"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="6"/>
-    </row>
-    <row r="65" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="D65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="6"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="66" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="D66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="6"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="6"/>
-    </row>
-    <row r="67" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="D67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="6"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="6"/>
-    </row>
-    <row r="68" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="D68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="6"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="6"/>
-    </row>
-    <row r="69" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="D69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="6"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="6"/>
-    </row>
-    <row r="70" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="D70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="6"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="6"/>
-    </row>
-    <row r="71" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="D71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="6"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="6"/>
-    </row>
-    <row r="72" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="8"/>
-      <c r="B72" s="8"/>
-      <c r="D72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="6"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="6"/>
-    </row>
-    <row r="73" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="8"/>
-      <c r="B73" s="8"/>
-      <c r="D73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="6"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="6"/>
-    </row>
-    <row r="74" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="8"/>
-      <c r="B74" s="8"/>
-      <c r="D74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="6"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="6"/>
-    </row>
-    <row r="75" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="8"/>
-      <c r="B75" s="8"/>
-      <c r="D75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="6"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="6"/>
-    </row>
-    <row r="76" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="8"/>
-      <c r="B76" s="8"/>
-      <c r="D76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="6"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="6"/>
-    </row>
-    <row r="77" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="8"/>
-      <c r="B77" s="8"/>
-      <c r="D77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="6"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="6"/>
-    </row>
-    <row r="78" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="8"/>
-      <c r="B78" s="8"/>
-      <c r="D78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="6"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="6"/>
-    </row>
-    <row r="79" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="8"/>
-      <c r="B79" s="8"/>
-      <c r="D79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="6"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="6"/>
-    </row>
-    <row r="80" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="8"/>
-      <c r="B80" s="8"/>
-      <c r="D80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="6"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="6"/>
-    </row>
-    <row r="81" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="D81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="6"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="6"/>
-    </row>
-    <row r="82" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="D82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="6"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="6"/>
-    </row>
-    <row r="83" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="8"/>
-      <c r="B83" s="8"/>
-      <c r="D83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="6"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="6"/>
-    </row>
-    <row r="84" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="8"/>
-      <c r="B84" s="8"/>
-      <c r="D84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="6"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="6"/>
-    </row>
-    <row r="85" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="8"/>
-      <c r="B85" s="8"/>
-      <c r="D85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="6"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="6"/>
-    </row>
-    <row r="86" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="8"/>
-      <c r="B86" s="8"/>
-      <c r="D86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="6"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="6"/>
-    </row>
-    <row r="87" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="8"/>
-      <c r="B87" s="8"/>
-      <c r="D87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="6"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="6"/>
-    </row>
-    <row r="88" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="8"/>
-      <c r="B88" s="8"/>
-      <c r="D88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="6"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="6"/>
-    </row>
-    <row r="89" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="8"/>
-      <c r="B89" s="8"/>
-      <c r="D89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="6"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="6"/>
-    </row>
-    <row r="90" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="8"/>
-      <c r="B90" s="8"/>
-      <c r="D90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="6"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="6"/>
-    </row>
-    <row r="91" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="8"/>
-      <c r="B91" s="8"/>
-      <c r="D91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="6"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="6"/>
-    </row>
-    <row r="92" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="8"/>
-      <c r="B92" s="8"/>
-      <c r="D92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="6"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="6"/>
-    </row>
-    <row r="93" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="8"/>
-      <c r="B93" s="8"/>
-      <c r="D93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="6"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="6"/>
-    </row>
-    <row r="94" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="8"/>
-      <c r="B94" s="8"/>
-      <c r="D94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="6"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="6"/>
-    </row>
-    <row r="95" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="8"/>
-      <c r="B95" s="8"/>
-      <c r="D95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="6"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="6"/>
-    </row>
-    <row r="96" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="8"/>
-      <c r="B96" s="8"/>
-      <c r="D96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="6"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="6"/>
-    </row>
-    <row r="97" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
-      <c r="D97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="6"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="6"/>
-    </row>
-    <row r="98" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="D98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="6"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="6"/>
-    </row>
-    <row r="99" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="8"/>
-      <c r="B99" s="8"/>
-      <c r="D99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="6"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="6"/>
-    </row>
-    <row r="100" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="8"/>
-      <c r="B100" s="8"/>
-      <c r="D100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="6"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="6"/>
-    </row>
-    <row r="101" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="8"/>
-      <c r="B101" s="8"/>
-      <c r="D101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="6"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="6"/>
-    </row>
-    <row r="102" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="8"/>
-      <c r="B102" s="8"/>
-      <c r="D102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="6"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="6"/>
-    </row>
-    <row r="103" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="8"/>
-      <c r="B103" s="8"/>
-      <c r="D103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="6"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="6"/>
-    </row>
-    <row r="104" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="8"/>
-      <c r="B104" s="8"/>
-      <c r="D104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="6"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="6"/>
-    </row>
-    <row r="105" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="8"/>
-      <c r="B105" s="8"/>
-      <c r="D105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="9"/>
-      <c r="H105" s="6"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="6"/>
-    </row>
-    <row r="106" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="8"/>
-      <c r="B106" s="8"/>
-      <c r="D106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="6"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="6"/>
-    </row>
-    <row r="107" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="8"/>
-      <c r="B107" s="8"/>
-      <c r="D107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="6"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="6"/>
-    </row>
-    <row r="108" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="8"/>
-      <c r="B108" s="8"/>
-      <c r="D108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="6"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="6"/>
-    </row>
-    <row r="109" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
-      <c r="D109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="6"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="6"/>
-    </row>
-    <row r="110" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="D110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="6"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="6"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A110 B3:B4">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CDBDD4D-5152-45A5-AC3F-19CAC06BB3C6}">
   <dimension ref="A1:L110"/>
   <sheetFormatPr defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -5920,6 +4660,1266 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A2:A110">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F98E668-5667-4278-8F3E-55E86133D308}">
+  <dimension ref="A1:L110"/>
+  <sheetFormatPr defaultRowHeight="14" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2">
+        <v>1450</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1908</v>
+      </c>
+      <c r="E2">
+        <v>2109</v>
+      </c>
+      <c r="F2" s="2">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="H2" s="6">
+        <v>46277</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="L2" s="6">
+        <v>46002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3">
+        <v>2100</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2450</v>
+      </c>
+      <c r="E3">
+        <v>2890</v>
+      </c>
+      <c r="F3" s="2">
+        <v>34</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="H3" s="6">
+        <v>46278</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="L3" s="6">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4">
+        <v>1400</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1679</v>
+      </c>
+      <c r="E4">
+        <v>1980</v>
+      </c>
+      <c r="F4" s="2">
+        <v>20</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="H4" s="6">
+        <v>46279</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="L4" s="6">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C5">
+        <v>2140</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2430</v>
+      </c>
+      <c r="E5">
+        <v>2560</v>
+      </c>
+      <c r="F5" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="H5" s="6">
+        <v>46280</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="L5" s="6">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6">
+        <v>120</v>
+      </c>
+      <c r="D6" s="2">
+        <v>230</v>
+      </c>
+      <c r="E6">
+        <v>340</v>
+      </c>
+      <c r="F6" s="2">
+        <v>9</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" s="6">
+        <v>46281</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="L6" s="6">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="D7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="6"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="D8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="6"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="D9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="6"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="D10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="6"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="D11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="6"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="D12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="6"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="D13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="6"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="D14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="6"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="D15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="6"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="D16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="6"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="D17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="6"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="6"/>
+    </row>
+    <row r="18" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="D18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="6"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="D19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="6"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="D20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="6"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="D21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="6"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="D22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="6"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="D23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="6"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="6"/>
+    </row>
+    <row r="24" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="D24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="6"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="6"/>
+    </row>
+    <row r="25" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="D25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="6"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="6"/>
+    </row>
+    <row r="26" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="D26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="6"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="6"/>
+    </row>
+    <row r="27" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="D27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="6"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="6"/>
+    </row>
+    <row r="28" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="D28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="6"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="6"/>
+    </row>
+    <row r="29" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="D29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="6"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="6"/>
+    </row>
+    <row r="30" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="D30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="6"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="D31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="6"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="6"/>
+    </row>
+    <row r="32" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="D32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="6"/>
+    </row>
+    <row r="33" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="D33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="D34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="D35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="D36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="6"/>
+    </row>
+    <row r="37" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="D37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="6"/>
+    </row>
+    <row r="38" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="D38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="6"/>
+    </row>
+    <row r="39" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="D39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="6"/>
+    </row>
+    <row r="40" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="D40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="6"/>
+    </row>
+    <row r="41" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="D41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="6"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="6"/>
+    </row>
+    <row r="42" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="D42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="6"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="6"/>
+    </row>
+    <row r="43" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="D43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="6"/>
+    </row>
+    <row r="44" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="D44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="6"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="6"/>
+    </row>
+    <row r="45" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="D45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="6"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="6"/>
+    </row>
+    <row r="46" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="D46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="6"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="6"/>
+    </row>
+    <row r="47" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="D47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="6"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="6"/>
+    </row>
+    <row r="48" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="D48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="6"/>
+    </row>
+    <row r="49" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="D49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="6"/>
+    </row>
+    <row r="50" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="D50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="6"/>
+    </row>
+    <row r="51" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="D51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="6"/>
+    </row>
+    <row r="52" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="D52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="6"/>
+    </row>
+    <row r="53" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="D53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="6"/>
+    </row>
+    <row r="54" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="D54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="6"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="6"/>
+    </row>
+    <row r="55" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="D55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="6"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="6"/>
+    </row>
+    <row r="56" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="D56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="6"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="6"/>
+    </row>
+    <row r="57" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="D57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="6"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="6"/>
+    </row>
+    <row r="58" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="D58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="6"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="6"/>
+    </row>
+    <row r="59" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="D59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="6"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="6"/>
+    </row>
+    <row r="60" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="D60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="6"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="6"/>
+    </row>
+    <row r="61" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="D61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="6"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="6"/>
+    </row>
+    <row r="62" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="D62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="6"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="6"/>
+    </row>
+    <row r="63" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="D63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="6"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="6"/>
+    </row>
+    <row r="64" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="D64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="6"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="6"/>
+    </row>
+    <row r="65" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="D65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="6"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="66" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="D66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="6"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="6"/>
+    </row>
+    <row r="67" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="D67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="6"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="6"/>
+    </row>
+    <row r="68" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="D68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="6"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="6"/>
+    </row>
+    <row r="69" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="D69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="6"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="6"/>
+    </row>
+    <row r="70" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="D70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="6"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="6"/>
+    </row>
+    <row r="71" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="D71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="6"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="6"/>
+    </row>
+    <row r="72" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="D72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="6"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="6"/>
+    </row>
+    <row r="73" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="D73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="6"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="6"/>
+    </row>
+    <row r="74" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="D74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="6"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="6"/>
+    </row>
+    <row r="75" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="D75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="6"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="6"/>
+    </row>
+    <row r="76" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="D76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="6"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="6"/>
+    </row>
+    <row r="77" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
+      <c r="D77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="6"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="6"/>
+    </row>
+    <row r="78" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
+      <c r="D78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="6"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="6"/>
+    </row>
+    <row r="79" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="D79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="6"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="6"/>
+    </row>
+    <row r="80" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="D80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="6"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="6"/>
+    </row>
+    <row r="81" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="D81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="6"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="6"/>
+    </row>
+    <row r="82" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="D82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="6"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="6"/>
+    </row>
+    <row r="83" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="D83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="6"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="6"/>
+    </row>
+    <row r="84" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="D84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="6"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="6"/>
+    </row>
+    <row r="85" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="D85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="6"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="6"/>
+    </row>
+    <row r="86" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="D86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="6"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="6"/>
+    </row>
+    <row r="87" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="D87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="6"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="6"/>
+    </row>
+    <row r="88" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="D88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="6"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="6"/>
+    </row>
+    <row r="89" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
+      <c r="D89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="6"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="6"/>
+    </row>
+    <row r="90" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
+      <c r="D90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="6"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="6"/>
+    </row>
+    <row r="91" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="D91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="6"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="6"/>
+    </row>
+    <row r="92" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="D92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="6"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="6"/>
+    </row>
+    <row r="93" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="8"/>
+      <c r="B93" s="8"/>
+      <c r="D93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="6"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="6"/>
+    </row>
+    <row r="94" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
+      <c r="D94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="6"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="6"/>
+    </row>
+    <row r="95" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
+      <c r="D95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="6"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="6"/>
+    </row>
+    <row r="96" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8"/>
+      <c r="D96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="6"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="6"/>
+    </row>
+    <row r="97" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="D97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="6"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="6"/>
+    </row>
+    <row r="98" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8"/>
+      <c r="D98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="6"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="6"/>
+    </row>
+    <row r="99" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="8"/>
+      <c r="B99" s="8"/>
+      <c r="D99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="6"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="6"/>
+    </row>
+    <row r="100" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="D100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="6"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="6"/>
+    </row>
+    <row r="101" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="8"/>
+      <c r="B101" s="8"/>
+      <c r="D101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="6"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="6"/>
+    </row>
+    <row r="102" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="8"/>
+      <c r="B102" s="8"/>
+      <c r="D102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="6"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="6"/>
+    </row>
+    <row r="103" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="D103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="6"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="6"/>
+    </row>
+    <row r="104" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="8"/>
+      <c r="B104" s="8"/>
+      <c r="D104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="9"/>
+      <c r="H104" s="6"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="6"/>
+    </row>
+    <row r="105" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="8"/>
+      <c r="B105" s="8"/>
+      <c r="D105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="6"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="6"/>
+    </row>
+    <row r="106" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
+      <c r="D106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="6"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="6"/>
+    </row>
+    <row r="107" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="D107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="6"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="6"/>
+    </row>
+    <row r="108" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="D108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="6"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="6"/>
+    </row>
+    <row r="109" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
+      <c r="D109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="6"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="6"/>
+    </row>
+    <row r="110" spans="1:12" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
+      <c r="D110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="6"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A110 B3:B4">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
